--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
@@ -129,12 +129,12 @@
     <t xml:space="preserve">San Bernardo</t>
   </si>
   <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
     <t xml:space="preserve">La Cisterna</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pudahuel</t>
   </si>
   <si>
@@ -180,12 +180,12 @@
     <t xml:space="preserve">La Reina</t>
   </si>
   <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vitacura</t>
   </si>
   <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Las Condes</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:36</t>
+    <t xml:space="preserve">2026-09-09 23:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1158,7 +1158,7 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>13109</v>
+        <v>13102</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2024</v>
@@ -1175,7 +1175,7 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>13102</v>
+        <v>13109</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2024</v>
@@ -1447,7 +1447,7 @@
         <v>54</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>13132</v>
+        <v>13120</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>2024</v>
@@ -1464,7 +1464,7 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>13120</v>
+        <v>13132</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:35</t>
+    <t xml:space="preserve">2026-09-17 14:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:29</t>
+    <t xml:space="preserve">2026-09-23 12:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:56</t>
+    <t xml:space="preserve">2026-10-01 23:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -232,9 +232,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1581,7 @@
         <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:24</t>
+    <t xml:space="preserve">2026-10-02 11:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:29</t>
+    <t xml:space="preserve">2026-10-02 15:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:18</t>
+    <t xml:space="preserve">2026-10-05 13:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
